--- a/data_raw/data_raw_2024_sheets/LTER4_OR_T03_2024.xlsx
+++ b/data_raw/data_raw_2024_sheets/LTER4_OR_T03_2024.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HLenihan 1/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryananderson/Reference/Bren/Coral Demography/data_raw/data_raw_2024_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8D8FC5-7FCD-AA46-B48F-5CA9444B71F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E52243-7197-3345-A56B-0A26F879B156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4400" yWindow="4800" windowWidth="37480" windowHeight="24000" xr2:uid="{F6C9647B-524A-6B4F-A5F9-4B995C3ABBEA}"/>
+    <workbookView xWindow="0" yWindow="560" windowWidth="29920" windowHeight="18780" xr2:uid="{F6C9647B-524A-6B4F-A5F9-4B995C3ABBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$P$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$P$42</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="62">
   <si>
     <t>LTER4</t>
   </si>
@@ -287,7 +287,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -458,30 +458,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFD4A6FF"/>
@@ -498,14 +474,14 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFF49900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -839,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A183C8-DAB7-6442-9F32-E549BA1F21B7}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
@@ -1087,28 +1063,28 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O7" t="s">
         <v>60</v>
@@ -1125,28 +1101,28 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E8">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O8" t="s">
         <v>60</v>
@@ -1163,28 +1139,28 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K9" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O9" t="s">
         <v>60</v>
@@ -1201,25 +1177,25 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E10">
-        <v>0.95</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F10">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -1242,25 +1218,25 @@
         <v>16</v>
       </c>
       <c r="E11">
-        <v>1.1499999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="F11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O11" t="s">
         <v>60</v>
@@ -1277,28 +1253,28 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="F12">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J12" t="s">
         <v>23</v>
       </c>
       <c r="K12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O12" t="s">
         <v>60</v>
@@ -1315,28 +1291,28 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E13">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F13">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
         <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K13" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="O13" t="s">
         <v>60</v>
@@ -1359,19 +1335,19 @@
         <v>1.9</v>
       </c>
       <c r="F14">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" t="s">
         <v>13</v>
-      </c>
-      <c r="J14" t="s">
-        <v>4</v>
       </c>
       <c r="K14" t="s">
         <v>19</v>
@@ -1394,28 +1370,37 @@
         <v>16</v>
       </c>
       <c r="E15">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F15">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I15" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>4</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
       </c>
       <c r="O15" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -1435,34 +1420,25 @@
         <v>2.1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16">
-        <v>3</v>
-      </c>
-      <c r="M16">
-        <v>4</v>
-      </c>
-      <c r="N16">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O16" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -1479,7 +1455,7 @@
         <v>16</v>
       </c>
       <c r="E17">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -1488,16 +1464,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="J17" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O17" t="s">
         <v>60</v>
@@ -1517,25 +1493,25 @@
         <v>16</v>
       </c>
       <c r="E18">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="F18">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O18" t="s">
         <v>60</v>
@@ -1555,25 +1531,25 @@
         <v>16</v>
       </c>
       <c r="E19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="F19">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I19" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O19" t="s">
         <v>60</v>
@@ -1593,25 +1569,25 @@
         <v>16</v>
       </c>
       <c r="E20">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I20" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J20" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K20" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O20" t="s">
         <v>60</v>
@@ -1628,28 +1604,28 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E21">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="F21">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O21" t="s">
         <v>60</v>
@@ -1666,28 +1642,28 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E22">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O22" t="s">
         <v>60</v>
@@ -1704,28 +1680,28 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E23">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F23">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O23" t="s">
         <v>60</v>
@@ -1742,28 +1718,28 @@
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="F24">
+        <v>75</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
         <v>30</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" t="s">
-        <v>20</v>
-      </c>
       <c r="K24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O24" t="s">
         <v>60</v>
@@ -1783,28 +1759,25 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="F25">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" t="s">
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>1.5</v>
+      </c>
+      <c r="O25" t="s">
         <v>17</v>
-      </c>
-      <c r="O25" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
@@ -1824,19 +1797,19 @@
         <v>0.6</v>
       </c>
       <c r="F26">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>1</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O26" t="s">
         <v>17</v>
@@ -1853,16 +1826,16 @@
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E27">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="F27">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>1</v>
@@ -1877,75 +1850,32 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28">
-        <v>4.8</v>
-      </c>
-      <c r="F28">
-        <v>80</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-      <c r="O28" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="A2:G2 I2:K2">
-    <cfRule type="containsText" dxfId="22" priority="17" operator="containsText" text="Missing data">
+    <cfRule type="beginsWith" dxfId="20" priority="16" operator="beginsWith" text="FI">
+      <formula>LEFT(A2,LEN("FI"))="FI"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="21" priority="16" operator="beginsWith" text="FI">
-      <formula>LEFT(A2,LEN("FI"))="FI"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:G2">
-    <cfRule type="beginsWith" dxfId="20" priority="14" operator="beginsWith" text="UK">
+    <cfRule type="beginsWith" dxfId="18" priority="14" operator="beginsWith" text="UK">
       <formula>LEFT(A2,LEN("UK"))="UK"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="19" priority="15" operator="beginsWith" text="FU">
+    <cfRule type="beginsWith" dxfId="17" priority="15" operator="beginsWith" text="FU">
       <formula>LEFT(A2,LEN("FU"))="FU"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:G28">
-    <cfRule type="expression" dxfId="18" priority="1">
-      <formula>A26="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
-      <formula>A26="Na"</formula>
+  <conditionalFormatting sqref="A25:G27 A3:K24">
+    <cfRule type="expression" dxfId="16" priority="1">
+      <formula>A3="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>A3="Na"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:K25">
-    <cfRule type="expression" dxfId="16" priority="18">
-      <formula>A3="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="19">
-      <formula>A3="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:K25">
+  <conditionalFormatting sqref="H3:K24">
     <cfRule type="containsText" dxfId="14" priority="20" operator="containsText" text=",">
       <formula>NOT(ISERROR(SEARCH(",", H3)))</formula>
     </cfRule>
